--- a/Buoi6_Nhom7.xlsx
+++ b/Buoi6_Nhom7.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\TH\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EB970171-9E07-4B06-A34E-1F0E985EF5A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E8A7BCC-9E05-4EE7-967E-2377FE342208}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{1F3F1EE5-5D42-498B-B26E-EA76E4329FCD}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="2" xr2:uid="{1F3F1EE5-5D42-498B-B26E-EA76E4329FCD}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="53">
   <si>
     <t>MSSV</t>
   </si>
@@ -203,7 +203,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -230,12 +230,6 @@
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -320,7 +314,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -345,12 +339,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -867,7 +855,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F7F4D0B-A383-4AB1-8C82-C1389183FFC4}">
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:C15"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11.7265625" customWidth="1"/>
@@ -1038,13 +1026,6 @@
         <v>32</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A16" s="9"/>
-      <c r="B16" s="10"/>
-      <c r="C16" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1052,7 +1033,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9DDDF390-E108-4020-94CB-8AE431FF1B3E}">
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11.08984375" customWidth="1"/>
@@ -1103,66 +1084,6 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A5" s="10"/>
-      <c r="B5" s="10"/>
-      <c r="C5" s="10"/>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A6" s="10"/>
-      <c r="B6" s="10"/>
-      <c r="C6" s="10"/>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A7" s="10"/>
-      <c r="B7" s="10"/>
-      <c r="C7" s="10"/>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A8" s="10"/>
-      <c r="B8" s="10"/>
-      <c r="C8" s="10"/>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A9" s="10"/>
-      <c r="B9" s="10"/>
-      <c r="C9" s="10"/>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A10" s="10"/>
-      <c r="B10" s="10"/>
-      <c r="C10" s="10"/>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A11" s="10"/>
-      <c r="B11" s="10"/>
-      <c r="C11" s="10"/>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A12" s="10"/>
-      <c r="B12" s="10"/>
-      <c r="C12" s="10"/>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A13" s="10"/>
-      <c r="B13" s="10"/>
-      <c r="C13" s="10"/>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A14" s="10"/>
-      <c r="B14" s="10"/>
-      <c r="C14" s="10"/>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A15" s="10"/>
-      <c r="B15" s="10"/>
-      <c r="C15" s="10"/>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A16" s="10"/>
-      <c r="B16" s="10"/>
-      <c r="C16" s="10"/>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
